--- a/exemple-ePrescription/ig/StructureDefinition-fr-pregnancy-history-document.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-pregnancy-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:50:30+00:00</t>
+    <t>2026-06-01T14:06:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
